--- a/artfynd/A 34104-2019 artfynd.xlsx
+++ b/artfynd/A 34104-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34104-2019 artfynd.xlsx
+++ b/artfynd/A 34104-2019 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>80565228</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556511.1884513756</v>
+        <v>556511</v>
       </c>
       <c r="R12" t="n">
-        <v>6946382.22227274</v>
+        <v>6946382</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1921,19 +1921,9 @@
           <t>2019-10-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-10-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2752,7 +2742,7 @@
         <v>80572235</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2789,10 +2779,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556523.9018366958</v>
+        <v>556524</v>
       </c>
       <c r="R20" t="n">
-        <v>6946393.019221779</v>
+        <v>6946393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,19 +2812,9 @@
           <t>2019-10-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2019-10-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4106,7 +4086,7 @@
         <v>80572238</v>
       </c>
       <c r="B32" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4143,10 +4123,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556505.7802436365</v>
+        <v>556506</v>
       </c>
       <c r="R32" t="n">
-        <v>6946375.230057711</v>
+        <v>6946375</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,19 +4156,9 @@
           <t>2019-10-19</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2019-10-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4554,7 +4524,7 @@
         <v>81134052</v>
       </c>
       <c r="B36" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4596,10 +4566,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556579.0920254065</v>
+        <v>556579</v>
       </c>
       <c r="R36" t="n">
-        <v>6946451.920630767</v>
+        <v>6946452</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4629,19 +4599,9 @@
           <t>2019-08-25</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2019-10-25</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5119,7 +5079,7 @@
         <v>81134057</v>
       </c>
       <c r="B41" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5161,10 +5121,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>556568.0866811071</v>
+        <v>556568</v>
       </c>
       <c r="R41" t="n">
-        <v>6946395.15472861</v>
+        <v>6946395</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5194,19 +5154,9 @@
           <t>2019-08-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2019-10-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5692,7 +5642,7 @@
         <v>87862996</v>
       </c>
       <c r="B46" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5733,10 +5683,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>556507.1115032875</v>
+        <v>556507</v>
       </c>
       <c r="R46" t="n">
-        <v>6946405.151824603</v>
+        <v>6946405</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5766,19 +5716,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6045,7 +5985,7 @@
         <v>87862886</v>
       </c>
       <c r="B49" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6086,10 +6026,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>556633.8604710542</v>
+        <v>556634</v>
       </c>
       <c r="R49" t="n">
-        <v>6946347.061810629</v>
+        <v>6946347</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6119,19 +6059,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -6282,7 +6212,7 @@
         <v>87862734</v>
       </c>
       <c r="B51" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6323,10 +6253,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>556578.2182396435</v>
+        <v>556578</v>
       </c>
       <c r="R51" t="n">
-        <v>6946449.145818677</v>
+        <v>6946449</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6356,19 +6286,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7337,7 +7257,7 @@
         <v>87862670</v>
       </c>
       <c r="B60" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7378,10 +7298,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>556508.0010768746</v>
+        <v>556508</v>
       </c>
       <c r="R60" t="n">
-        <v>6946407.006956702</v>
+        <v>6946407</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7411,19 +7331,9 @@
           <t>2020-09-05</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -8735,7 +8645,7 @@
         <v>96080393</v>
       </c>
       <c r="B72" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8776,10 +8686,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>556722.3465652817</v>
+        <v>556723</v>
       </c>
       <c r="R72" t="n">
-        <v>6946317.758819449</v>
+        <v>6946318</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8809,19 +8719,9 @@
           <t>2021-09-12</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -10965,7 +10865,7 @@
         <v>102450629</v>
       </c>
       <c r="B91" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11006,10 +10906,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>556448.5334230716</v>
+        <v>556449</v>
       </c>
       <c r="R91" t="n">
-        <v>6946409.671140439</v>
+        <v>6946409</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -11039,19 +10939,9 @@
           <t>2022-07-24</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2022-07-24</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">

--- a/artfynd/A 34104-2019 artfynd.xlsx
+++ b/artfynd/A 34104-2019 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>80565228</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>80572235</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>80572238</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>81134052</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>81134057</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>87862996</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>87862886</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>87862734</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>87862670</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>96080393</v>
       </c>
       <c r="B72" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>102450629</v>
       </c>
       <c r="B91" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>

--- a/artfynd/A 34104-2019 artfynd.xlsx
+++ b/artfynd/A 34104-2019 artfynd.xlsx
@@ -1847,7 +1847,7 @@
         <v>80565228</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>80572235</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>80572238</v>
       </c>
       <c r="B32" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>81134052</v>
       </c>
       <c r="B36" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>81134057</v>
       </c>
       <c r="B41" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>87862996</v>
       </c>
       <c r="B46" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>87862886</v>
       </c>
       <c r="B49" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>87862734</v>
       </c>
       <c r="B51" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>87862670</v>
       </c>
       <c r="B60" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>96080393</v>
       </c>
       <c r="B72" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>102450629</v>
       </c>
       <c r="B91" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
